--- a/output/metadata_parse/all_tables_metadata.xlsx
+++ b/output/metadata_parse/all_tables_metadata.xlsx
@@ -426,24 +426,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,55 +470,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>表行数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>字段注释</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>字段注释填充</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>是否为空</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>主键</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>外键</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>外键引用</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>字段空值率</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>字段角色</t>
         </is>
@@ -544,45 +550,48 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>coupon_id</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>优惠券ID</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -609,45 +618,48 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>coupon_name</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>优惠券名称</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -674,53 +686,56 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>discount_type</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1满减 2折扣</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1满减 2折扣</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -747,49 +762,52 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>min_amount</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>最小金额</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -816,49 +834,52 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>discount_amount</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>折扣金额</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -885,45 +906,48 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -950,45 +974,48 @@
           <t>优惠券表</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1015,49 +1042,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -1084,49 +1114,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1153,49 +1186,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>shop_id</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1222,49 +1258,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>order_status</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>订单状态 1待支付 2已支付 3已发货 4已完成 5已取消</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>订单状态 1待支付 2已支付 3已发货 4已完成 5已取消</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1291,49 +1330,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>订单总金额</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>订单总金额</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1360,49 +1402,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>pay_amount</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>实付金额</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>实付金额</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1429,49 +1474,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>discount_amount</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>优惠金额</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>优惠金额</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1498,49 +1546,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>order_time</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>下单时间</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>下单时间</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1567,49 +1618,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>pay_time</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>支付时间</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>支付时间</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>14.50%</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1636,49 +1690,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>is_deleted</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>是否删除</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1705,49 +1762,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1774,49 +1834,52 @@
           <t>订单主表</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>update_time</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1843,45 +1906,48 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -1908,49 +1974,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1977,49 +2046,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2046,49 +2118,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>sku_name</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>varchar(255)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -2115,49 +2190,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>购买数量</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>购买数量</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>int(11)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2184,49 +2262,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>original_amount</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>原价金额</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>原价金额</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2253,49 +2334,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>split_amount</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>分摊金额</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>分摊金额</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2322,49 +2406,52 @@
           <t>订单明细表</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>7512</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -2391,45 +2478,48 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>pay_id</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>支付ID</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -2456,45 +2546,48 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -2521,45 +2614,48 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2586,49 +2682,52 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>pay_type</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>支付方式 支付宝/微信/银行卡</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>支付方式 支付宝/微信/银行卡</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -2655,49 +2754,52 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>pay_amount</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>支付金额</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>支付金额</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2724,53 +2826,56 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>pay_status</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>1成功 2失败</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>1成功 2失败</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2797,45 +2902,48 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>pay_time</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>支付时间</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -2862,49 +2970,52 @@
           <t>支付信息表</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -2931,45 +3042,48 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>251</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>refund_id</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>退款ID</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -2996,45 +3110,48 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>251</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3061,45 +3178,48 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>251</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3126,45 +3246,48 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>251</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>SKUID</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3191,49 +3314,52 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>251</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>refund_amount</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>退款金额</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>退款金额</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3260,53 +3386,56 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>251</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>refund_status</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>0申请中 1成功 2拒绝</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>0申请中 1成功 2拒绝</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3333,45 +3462,48 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>251</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>refund_time</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>退款时间</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3398,49 +3530,52 @@
           <t>退款表</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>251</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -3467,49 +3602,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>shop_id</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3536,49 +3674,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>shop_name</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>门店名称</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>门店名称</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3605,49 +3746,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>city_id</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>城市ID</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>城市ID</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3674,49 +3818,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>city_name</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>城市名称</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>城市名称</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -3743,49 +3890,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>manager_name</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>店长</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>店长</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -3812,53 +3962,56 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>is_open</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>是否营业</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>是否营业</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3885,49 +4038,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -3954,49 +4110,52 @@
           <t>门店信息表</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>update_time</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4023,49 +4182,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" t="n">
+        <v>500</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>商品SKU ID</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>商品SKU ID</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4092,49 +4254,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="n">
+        <v>500</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>spu_id</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>SPU ID</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>SPU ID</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4161,49 +4326,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="n">
+        <v>500</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>sku_name</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>varchar(255)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -4230,49 +4398,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" t="n">
+        <v>500</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>category_id</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>品类ID</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>品类ID</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4299,49 +4470,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="n">
+        <v>500</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>category_name</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>品类名称</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>品类名称</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -4368,49 +4542,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="n">
+        <v>500</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>shop_id</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4437,49 +4614,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" t="n">
+        <v>500</v>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>cost_price</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>成本价</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>成本价</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4506,49 +4686,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="n">
+        <v>500</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>sale_price</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>销售价</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>销售价</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4575,53 +4758,56 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" t="n">
+        <v>500</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>is_on_sale</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>是否上架</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>是否上架</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4648,49 +4834,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" t="n">
+        <v>500</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>is_deleted</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>是否删除</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4717,49 +4906,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="n">
+        <v>500</v>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4786,49 +4978,52 @@
           <t>商品SKU表</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="n">
+        <v>500</v>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>update_time</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4855,45 +5050,48 @@
           <t>商品库存表</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4920,45 +5118,48 @@
           <t>商品库存表</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
         <is>
           <t>SKUID</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4985,45 +5186,48 @@
           <t>商品库存表</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>shop_id</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5050,53 +5254,56 @@
           <t>商品库存表</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>stock_num</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>库存数量</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>库存数量</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>int(11)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5123,49 +5330,52 @@
           <t>商品库存表</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>update_time</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -5192,45 +5402,48 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5257,45 +5470,48 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5322,45 +5538,48 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>coupon_id</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
         <is>
           <t>优惠券ID</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5387,49 +5606,52 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>使用订单ID</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>使用订单ID</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
         <is>
           <t>35.74%</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5456,53 +5678,56 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>use_status</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>0未使用 1已使用 2已过期</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>0未使用 1已使用 2已过期</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5529,49 +5754,52 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -5598,45 +5826,48 @@
           <t>用户优惠券表</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>use_time</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
         <is>
           <t>使用时间</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
         <is>
           <t>35.74%</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -5663,49 +5894,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5732,49 +5966,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>user_name</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>用户名</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>用户名</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t>business_attr</t>
         </is>
@@ -5801,49 +6038,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>性别 1男 2女</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>性别 1男 2女</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -5870,49 +6110,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>手机号</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>手机号</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5939,49 +6182,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>register_time</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>注册时间</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>注册时间</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -6008,49 +6254,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>register_channel</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>注册渠道</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>注册渠道</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -6077,49 +6326,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>city_name</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>所在城市</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>所在城市</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -6146,53 +6398,56 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>is_deleted</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>是否删除</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>是否删除</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -6219,49 +6474,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>create_time</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -6288,49 +6546,52 @@
           <t>用户基础信息表</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>update_time</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>

--- a/output/metadata_parse/all_tables_metadata.xlsx
+++ b/output/metadata_parse/all_tables_metadata.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="所有表元数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="所有表元数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/metadata_parse/all_tables_metadata.xlsx
+++ b/output/metadata_parse/all_tables_metadata.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -437,14 +437,15 @@
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,40 +491,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>字段注释AI推荐</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>是否为空</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>主键</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>外键</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>外键引用</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>字段空值率</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>字段角色</t>
         </is>
@@ -566,32 +572,37 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>优惠券ID</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -634,32 +645,37 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>优惠券名称</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -706,36 +722,41 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>折扣类型</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -778,36 +799,41 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>最小金额</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -850,36 +876,41 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>折扣金额</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -922,32 +953,37 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>开始时间</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -990,32 +1026,37 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>结束时间</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1062,32 +1103,37 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -1134,32 +1180,37 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1206,32 +1257,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>门店ID</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1278,32 +1334,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1350,32 +1411,37 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>总计金额</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1422,32 +1488,37 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>支付金额</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1494,32 +1565,37 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>折扣金额</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -1566,32 +1642,37 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>订单时间</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1638,32 +1719,37 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>支付时间</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>14.50%</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -1706,36 +1792,41 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1778,36 +1869,41 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1850,36 +1946,41 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -1922,32 +2023,37 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>订单项ID</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -1994,32 +2100,37 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2066,32 +2177,37 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>商品单位ID</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2138,32 +2254,37 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>商品单位名称</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>varchar(255)</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -2210,32 +2331,37 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>int(11)</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2282,32 +2408,37 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>原始金额</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2354,32 +2485,37 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>拆分金额</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2422,36 +2558,41 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -2494,32 +2635,37 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>支付ID</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -2562,32 +2708,37 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -2630,32 +2781,37 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2702,32 +2858,37 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>支付类型</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -2774,32 +2935,37 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>支付金额</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2846,36 +3012,41 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>支付状态</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -2918,32 +3089,37 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>支付时间</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -2986,36 +3162,41 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -3058,32 +3239,37 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>退款ID</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3126,32 +3312,37 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3194,32 +3385,37 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3257,37 +3453,42 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SKUID</t>
+          <t>商品单位ID</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>商品单位ID</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3334,32 +3535,37 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>退款金额</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3406,36 +3612,41 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>退款状态</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3478,32 +3689,37 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>退款时间</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3546,36 +3762,41 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -3622,32 +3843,37 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>门店ID</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3694,32 +3920,37 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>门店名称</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -3766,32 +3997,37 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>城市ID</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -3838,32 +4074,37 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>城市名称</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -3910,32 +4151,37 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>经理名称</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -3982,36 +4228,41 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>是否开放</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4054,36 +4305,41 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4126,36 +4382,41 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4202,32 +4463,37 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>商品单位ID</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4274,32 +4540,37 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4346,32 +4617,37 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t>商品单位名称</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>varchar(255)</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -4418,32 +4694,37 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>分类ID</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4490,32 +4771,37 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>分类名称</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -4562,32 +4848,37 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>门店ID</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4634,32 +4925,37 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>成本价格</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4706,32 +5002,37 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>销售价格</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>decimal(16,2)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4778,36 +5079,41 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>是否在销售</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -4850,36 +5156,41 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4922,36 +5233,41 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -4994,36 +5310,41 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -5066,32 +5387,37 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>库存信息ID</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5129,37 +5455,42 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SKUID</t>
+          <t>商品单位ID</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>商品单位ID</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5202,32 +5533,37 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t>门店ID</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5274,36 +5610,41 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
+          <t>库存号码</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>int(11)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5346,36 +5687,41 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -5418,32 +5764,37 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>用户优惠券ID</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5486,32 +5837,37 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5554,32 +5910,37 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>优惠券ID</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5626,32 +5987,37 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
         <is>
           <t>35.74%</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5698,36 +6064,41 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>使用状态</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>numeric_measure</t>
         </is>
@@ -5770,36 +6141,41 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -5842,32 +6218,37 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>使用时间</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
         <is>
           <t>35.74%</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>business_time</t>
         </is>
@@ -5914,32 +6295,37 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>bigint(20)</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -5986,32 +6372,37 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t>用户名称</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>business_attr</t>
         </is>
@@ -6058,32 +6449,37 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>性别</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>char(1)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -6130,32 +6526,37 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -6202,32 +6603,37 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
+          <t>注册时间</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -6274,32 +6680,37 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>注册渠道</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -6346,32 +6757,37 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>城市名称</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>low_cardinality</t>
         </is>
@@ -6418,36 +6834,41 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>tinyint(4)</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -6490,36 +6911,41 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>tech_meta</t>
         </is>
@@ -6562,38 +6988,1839 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>tech_meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bigint(20)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>primary_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>用户名</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>用户名称</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>性别 1男 2女</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>性别 1男 2女</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>性别</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>char(1)</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>register_time</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>注册时间</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>注册时间</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>注册时间</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>business_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>register_channel</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>注册渠道</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>注册渠道</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>注册渠道</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>city_name</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>所在城市</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>所在城市</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>城市名称</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>是否删除</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>tinyint(4)</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>tech_meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>create_time</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>tech_meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>update_time</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>tech_meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Column1222</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>列1222</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>列1222</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>is_number</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>是否号码</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>是否号码</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>is_bool</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>是否布尔</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>是否布尔</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AzZZAA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>azzzaa</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>azzzaa</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>inner</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>拆分</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>拆分</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>fetch</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>获取</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>获取</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>xxxxx</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>xxxxx</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>xxxxx</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>coupon</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>优惠券</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>优惠券</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>sold</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>interpreter</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>解释器</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>解释器</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>mall_oltp</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>user_info_1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>浏览器</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>浏览器</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>low_cardinality</t>
         </is>
       </c>
     </row>
